--- a/docs/evaluation/assistant-prompt-tests.xlsx
+++ b/docs/evaluation/assistant-prompt-tests.xlsx
@@ -528,7 +528,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Before testing: run hosted scripts 11, 12, 13 and 14 in Supabase (backend/supabase/hosted), then restart the backend.</t>
+          <t>Before testing: run hosted scripts 11 to 15 in Supabase (backend/supabase/hosted), then restart the backend.</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Lost-card safety steps plus "I've also passed this to our fraud team as urgent (reference TCK-...)". Shows in My requests as Card reported lost or stolen.</t>
+          <t>Lost-card safety steps first, then "Would you like me to report this to our fraud team as urgent now?" with Yes, report my card / No buttons. No ticket yet.</t>
         </is>
       </c>
       <c r="G20" s="5" t="n"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>"You already have an open lost-card report" with the SAME reference as row 19.</t>
+          <t>Safety steps and the same offer. After "Yes, report my card": "You already have an open lost-card report" with the SAME reference (if row 19 was reported).</t>
         </is>
       </c>
       <c r="G21" s="5" t="n"/>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Says it cannot help with that here and passes it to her relationship manager, with a TCK- reference. Ticket topic: Fees or rates.</t>
+          <t>Shows "Here’s what I’d send to your relationship manager" (topic Fees or rates, her question) with Send to my RM / Cancel buttons. Nothing is created until she taps Send; then a TCK- reference.</t>
         </is>
       </c>
       <c r="G22" s="5" t="n"/>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>"You already have an open request about this ... I've added your question to it" with the SAME reference as row 21. My requests shows "You added: ...".</t>
+          <t>Preview says she already has an open request about this (the fee ticket) with Add to TCK-… / Open a new request / Cancel. Add → "I’ve added your question to it"; Open a new request → a new reference.</t>
         </is>
       </c>
       <c r="G23" s="5" t="n"/>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Passed to her relationship manager (topic: Complex transfer) with a TCK- reference.</t>
+          <t>Preview (topic Complex transfer) with Send to my RM / Cancel; after Send, a TCK- reference.</t>
         </is>
       </c>
       <c r="G24" s="5" t="n"/>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>"Of course. I've passed your question to your relationship manager" with a TCK- reference (or the existing one).</t>
+          <t>"Of course." plus the preview ("You asked to speak with your relationship manager", earlier messages) and Send to my RM / Cancel.</t>
         </is>
       </c>
       <c r="G26" s="5" t="n"/>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Does not give advice; passes it to her relationship manager (topic: Investment or product advice).</t>
+          <t>Does not give advice; shows the preview (topic Investment or product advice). After Send, a NEW reference (different topic from the fee ticket).</t>
         </is>
       </c>
       <c r="G27" s="5" t="n"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Only approved information. No invented rates.</t>
+          <t>Home loans, personal loans and car loans from DemoBank articles; no invented rates or amounts.</t>
         </is>
       </c>
       <c r="G29" s="5" t="n"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>General criteria only; does not say yes or no; the bank decides.</t>
+          <t>General criteria from the DemoBank Personal loans article (21+, regular income, ID and proof of income); does not say yes or no; the bank decides.</t>
         </is>
       </c>
       <c r="G30" s="5" t="n"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Says the bank makes the final decision; no promise.</t>
+          <t>From the Home loans article: the bank assesses and decides; no promise of approval, rate or date.</t>
         </is>
       </c>
       <c r="G32" s="5" t="n"/>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>RM ticket A (topic Fees or rates) with a TCK- reference.</t>
+          <t>Shows "Here’s what I’d send to your relationship manager" (topic Fees or rates, her question) with Send to my RM / Cancel buttons. Nothing is created until she taps Send; then a TCK- reference.</t>
         </is>
       </c>
       <c r="G42" s="6" t="n"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>A NEW, different TCK- reference (topic Investment or product advice), not the fee ticket.</t>
+          <t>Does not give advice; shows the preview (topic Investment or product advice). After Send, a NEW reference (different topic from the fee ticket).</t>
         </is>
       </c>
       <c r="G43" s="6" t="n"/>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Another new TCK- reference (a general question for the RM), or the matching open one if you already have one.</t>
+          <t>"Of course." plus the preview ("You asked to speak with your relationship manager", earlier messages) and Send to my RM / Cancel.</t>
         </is>
       </c>
       <c r="G44" s="6" t="n"/>
@@ -2063,10 +2063,280 @@
       <c r="H45" s="6" t="n"/>
       <c r="I45" s="6" t="n"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>RM handover (CR8)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Same chat as any preview</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>no dont send</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>"No problem, nothing has been sent to your relationship manager." No new request in My requests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cards (CR14)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Same chat as row 5</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>what about the due date?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>and the limit?</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Answers for the Travel Card ending 5592 (due 25 Nov 2026) without asking which card again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Lost card (CR12)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Same chat as row 19</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Tap "Yes, report my card"</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>yes pls</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>"I’ve passed this to our fraud team as urgent (reference TCK-…)". My requests shows Card reported lost or stolen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lost card (CR12)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>New chat: type row 19 first</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>not now</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>"Okay, I haven’t reported it" plus a reminder to call the fraud line. No ticket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Navigation (CR2)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New chat</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>whats my travel card balance</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>show my recent transactions</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Answer ends with a "Go to Cards" (or "Go to Recent activity") button that opens Overview at that section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Login (CR1)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sign-in page</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Click "Forgot password?"</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Shows reset guidance (official app/website or client services) and says no one will ask for her password.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Login (CR1)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sign-in page</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sign in with a wrong password</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>wrong email</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>"Incorrect email or password. Please try again." (same message either way)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Card limit (CR11)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>New chat</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>i want to raise my card limit to $15,000, then: actually make it 12000</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>raise limit 20k</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tap "Raise a card limit request": the form summary says "Requested new limit: SGD 12,000 (corrected from SGD 15,000)".</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RM handover (CR8)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Any chat with an open request</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>talk to a person</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>The preview also lists "Open requests: TCK-… (status)" so the RM sees previous actions.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I45"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,Partly,No"</formula1>
     </dataValidation>
   </dataValidations>
